--- a/services/platform-api/src/main/resources/templates/培训考勤表.xlsx
+++ b/services/platform-api/src/main/resources/templates/培训考勤表.xlsx
@@ -497,7 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>序号</t>
@@ -554,7 +554,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>

--- a/services/platform-api/src/main/resources/templates/培训考勤表.xlsx
+++ b/services/platform-api/src/main/resources/templates/培训考勤表.xlsx
@@ -65,16 +65,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FF000000"/>
       </bottom>
     </border>
   </borders>
@@ -89,10 +89,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyBorder="1" numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyBorder="1" numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
